--- a/07.머신러닝/지도학습/02.분류/02.KNN/penguin.xlsx
+++ b/07.머신러닝/지도학습/02.분류/02.KNN/penguin.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G345"/>
+  <dimension ref="A1:G343"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,11 +551,23 @@
           <t>Torgersen</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>193</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3450</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -569,20 +581,20 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36.7</v>
+        <v>39.3</v>
       </c>
       <c r="D6" t="n">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="E6" t="n">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F6" t="n">
-        <v>3450</v>
+        <v>3650</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -598,20 +610,20 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>39.3</v>
+        <v>38.9</v>
       </c>
       <c r="D7" t="n">
-        <v>20.6</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="F7" t="n">
-        <v>3650</v>
+        <v>3625</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -627,20 +639,20 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38.9</v>
+        <v>39.2</v>
       </c>
       <c r="D8" t="n">
-        <v>17.8</v>
+        <v>19.6</v>
       </c>
       <c r="E8" t="n">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="F8" t="n">
-        <v>3625</v>
+        <v>4675</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -656,22 +668,18 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>39.2</v>
+        <v>34.1</v>
       </c>
       <c r="D9" t="n">
-        <v>19.6</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F9" t="n">
-        <v>4675</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
+        <v>3475</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -685,16 +693,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>34.1</v>
+        <v>42</v>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>20.2</v>
       </c>
       <c r="E10" t="n">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F10" t="n">
-        <v>3475</v>
+        <v>4250</v>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
@@ -710,16 +718,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>42</v>
+        <v>37.8</v>
       </c>
       <c r="D11" t="n">
-        <v>20.2</v>
+        <v>17.1</v>
       </c>
       <c r="E11" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F11" t="n">
-        <v>4250</v>
+        <v>3300</v>
       </c>
       <c r="G11" t="inlineStr"/>
     </row>
@@ -738,13 +746,13 @@
         <v>37.8</v>
       </c>
       <c r="D12" t="n">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="E12" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F12" t="n">
-        <v>3300</v>
+        <v>3700</v>
       </c>
       <c r="G12" t="inlineStr"/>
     </row>
@@ -760,18 +768,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>37.8</v>
+        <v>41.1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.3</v>
+        <v>17.6</v>
       </c>
       <c r="E13" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F13" t="n">
-        <v>3700</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
+        <v>3200</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -785,20 +797,20 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>41.1</v>
+        <v>38.6</v>
       </c>
       <c r="D14" t="n">
-        <v>17.6</v>
+        <v>21.2</v>
       </c>
       <c r="E14" t="n">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="F14" t="n">
-        <v>3200</v>
+        <v>3800</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -814,16 +826,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>38.6</v>
+        <v>34.6</v>
       </c>
       <c r="D15" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="E15" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="F15" t="n">
-        <v>3800</v>
+        <v>4400</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -843,20 +855,20 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>34.6</v>
+        <v>36.6</v>
       </c>
       <c r="D16" t="n">
-        <v>21.1</v>
+        <v>17.8</v>
       </c>
       <c r="E16" t="n">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="F16" t="n">
-        <v>4400</v>
+        <v>3700</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -872,16 +884,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>36.6</v>
+        <v>38.7</v>
       </c>
       <c r="D17" t="n">
-        <v>17.8</v>
+        <v>19</v>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="F17" t="n">
-        <v>3700</v>
+        <v>3450</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -901,20 +913,20 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>38.7</v>
+        <v>42.5</v>
       </c>
       <c r="D18" t="n">
-        <v>19</v>
+        <v>20.7</v>
       </c>
       <c r="E18" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F18" t="n">
-        <v>3450</v>
+        <v>4500</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -930,20 +942,20 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>42.5</v>
+        <v>34.4</v>
       </c>
       <c r="D19" t="n">
-        <v>20.7</v>
+        <v>18.4</v>
       </c>
       <c r="E19" t="n">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="F19" t="n">
-        <v>4500</v>
+        <v>3325</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -959,20 +971,20 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>34.4</v>
+        <v>46</v>
       </c>
       <c r="D20" t="n">
-        <v>18.4</v>
+        <v>21.5</v>
       </c>
       <c r="E20" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="F20" t="n">
-        <v>3325</v>
+        <v>4200</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -984,24 +996,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>46</v>
+        <v>37.8</v>
       </c>
       <c r="D21" t="n">
-        <v>21.5</v>
+        <v>18.3</v>
       </c>
       <c r="E21" t="n">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="F21" t="n">
-        <v>4200</v>
+        <v>3400</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1017,20 +1029,20 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="D22" t="n">
-        <v>18.3</v>
+        <v>18.7</v>
       </c>
       <c r="E22" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="F22" t="n">
-        <v>3400</v>
+        <v>3600</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1046,20 +1058,20 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>37.7</v>
+        <v>35.9</v>
       </c>
       <c r="D23" t="n">
-        <v>18.7</v>
+        <v>19.2</v>
       </c>
       <c r="E23" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="F23" t="n">
-        <v>3600</v>
+        <v>3800</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1075,20 +1087,20 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>35.9</v>
+        <v>38.2</v>
       </c>
       <c r="D24" t="n">
-        <v>19.2</v>
+        <v>18.1</v>
       </c>
       <c r="E24" t="n">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F24" t="n">
-        <v>3800</v>
+        <v>3950</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1104,16 +1116,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>38.2</v>
+        <v>38.8</v>
       </c>
       <c r="D25" t="n">
-        <v>18.1</v>
+        <v>17.2</v>
       </c>
       <c r="E25" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F25" t="n">
-        <v>3950</v>
+        <v>3800</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1133,20 +1145,20 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>38.8</v>
+        <v>35.3</v>
       </c>
       <c r="D26" t="n">
-        <v>17.2</v>
+        <v>18.9</v>
       </c>
       <c r="E26" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="F26" t="n">
         <v>3800</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1162,20 +1174,20 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>35.3</v>
+        <v>40.6</v>
       </c>
       <c r="D27" t="n">
-        <v>18.9</v>
+        <v>18.6</v>
       </c>
       <c r="E27" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F27" t="n">
-        <v>3800</v>
+        <v>3550</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1191,20 +1203,20 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>40.6</v>
+        <v>40.5</v>
       </c>
       <c r="D28" t="n">
-        <v>18.6</v>
+        <v>17.9</v>
       </c>
       <c r="E28" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="F28" t="n">
-        <v>3550</v>
+        <v>3200</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1220,16 +1232,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>40.5</v>
+        <v>37.9</v>
       </c>
       <c r="D29" t="n">
-        <v>17.9</v>
+        <v>18.6</v>
       </c>
       <c r="E29" t="n">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="F29" t="n">
-        <v>3200</v>
+        <v>3150</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1249,20 +1261,20 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>37.9</v>
+        <v>40.5</v>
       </c>
       <c r="D30" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
       <c r="E30" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="F30" t="n">
-        <v>3150</v>
+        <v>3950</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1274,24 +1286,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>40.5</v>
+        <v>39.5</v>
       </c>
       <c r="D31" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E31" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F31" t="n">
-        <v>3950</v>
+        <v>3250</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1307,20 +1319,20 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>39.5</v>
+        <v>37.2</v>
       </c>
       <c r="D32" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E32" t="n">
         <v>178</v>
       </c>
       <c r="F32" t="n">
-        <v>3250</v>
+        <v>3900</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1336,20 +1348,20 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37.2</v>
+        <v>39.5</v>
       </c>
       <c r="D33" t="n">
-        <v>18.1</v>
+        <v>17.8</v>
       </c>
       <c r="E33" t="n">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="F33" t="n">
-        <v>3900</v>
+        <v>3300</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1365,20 +1377,20 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>39.5</v>
+        <v>40.9</v>
       </c>
       <c r="D34" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E34" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F34" t="n">
-        <v>3300</v>
+        <v>3900</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1394,20 +1406,20 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>40.9</v>
+        <v>36.4</v>
       </c>
       <c r="D35" t="n">
-        <v>18.9</v>
+        <v>17</v>
       </c>
       <c r="E35" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="F35" t="n">
-        <v>3900</v>
+        <v>3325</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1423,20 +1435,20 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>36.4</v>
+        <v>39.2</v>
       </c>
       <c r="D36" t="n">
-        <v>17</v>
+        <v>21.1</v>
       </c>
       <c r="E36" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F36" t="n">
-        <v>3325</v>
+        <v>4150</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1452,16 +1464,16 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>39.2</v>
+        <v>38.8</v>
       </c>
       <c r="D37" t="n">
-        <v>21.1</v>
+        <v>20</v>
       </c>
       <c r="E37" t="n">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="F37" t="n">
-        <v>4150</v>
+        <v>3950</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1481,20 +1493,20 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>38.8</v>
+        <v>42.2</v>
       </c>
       <c r="D38" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="E38" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="F38" t="n">
-        <v>3950</v>
+        <v>3550</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1510,16 +1522,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>42.2</v>
+        <v>37.6</v>
       </c>
       <c r="D39" t="n">
-        <v>18.5</v>
+        <v>19.3</v>
       </c>
       <c r="E39" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F39" t="n">
-        <v>3550</v>
+        <v>3300</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1539,20 +1551,20 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>37.6</v>
+        <v>39.8</v>
       </c>
       <c r="D40" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="E40" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F40" t="n">
-        <v>3300</v>
+        <v>4650</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1568,20 +1580,20 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>39.8</v>
+        <v>36.5</v>
       </c>
       <c r="D41" t="n">
-        <v>19.1</v>
+        <v>18</v>
       </c>
       <c r="E41" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F41" t="n">
-        <v>4650</v>
+        <v>3150</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1597,20 +1609,20 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>36.5</v>
+        <v>40.8</v>
       </c>
       <c r="D42" t="n">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="E42" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="F42" t="n">
-        <v>3150</v>
+        <v>3900</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1626,20 +1638,20 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>40.8</v>
+        <v>36</v>
       </c>
       <c r="D43" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="E43" t="n">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="F43" t="n">
-        <v>3900</v>
+        <v>3100</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1655,20 +1667,20 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>36</v>
+        <v>44.1</v>
       </c>
       <c r="D44" t="n">
-        <v>18.5</v>
+        <v>19.7</v>
       </c>
       <c r="E44" t="n">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="F44" t="n">
-        <v>3100</v>
+        <v>4400</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1684,20 +1696,20 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>44.1</v>
+        <v>37</v>
       </c>
       <c r="D45" t="n">
-        <v>19.7</v>
+        <v>16.9</v>
       </c>
       <c r="E45" t="n">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F45" t="n">
-        <v>4400</v>
+        <v>3000</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1713,20 +1725,20 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>37</v>
+        <v>39.6</v>
       </c>
       <c r="D46" t="n">
-        <v>16.9</v>
+        <v>18.8</v>
       </c>
       <c r="E46" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F46" t="n">
-        <v>3000</v>
+        <v>4600</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1742,16 +1754,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>39.6</v>
+        <v>41.1</v>
       </c>
       <c r="D47" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="E47" t="n">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F47" t="n">
-        <v>4600</v>
+        <v>3425</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1771,22 +1783,18 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>41.1</v>
+        <v>37.5</v>
       </c>
       <c r="D48" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="E48" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F48" t="n">
-        <v>3425</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
+        <v>2975</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1800,18 +1808,22 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="D49" t="n">
-        <v>18.9</v>
+        <v>17.9</v>
       </c>
       <c r="E49" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="F49" t="n">
-        <v>2975</v>
-      </c>
-      <c r="G49" t="inlineStr"/>
+        <v>3450</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1825,20 +1837,20 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>36</v>
+        <v>42.3</v>
       </c>
       <c r="D50" t="n">
-        <v>17.9</v>
+        <v>21.2</v>
       </c>
       <c r="E50" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F50" t="n">
-        <v>3450</v>
+        <v>4150</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1850,24 +1862,24 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>42.3</v>
+        <v>39.6</v>
       </c>
       <c r="D51" t="n">
-        <v>21.2</v>
+        <v>17.7</v>
       </c>
       <c r="E51" t="n">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F51" t="n">
-        <v>4150</v>
+        <v>3500</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1883,20 +1895,20 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>39.6</v>
+        <v>40.1</v>
       </c>
       <c r="D52" t="n">
-        <v>17.7</v>
+        <v>18.9</v>
       </c>
       <c r="E52" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F52" t="n">
-        <v>3500</v>
+        <v>4300</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1912,20 +1924,20 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>40.1</v>
+        <v>35</v>
       </c>
       <c r="D53" t="n">
-        <v>18.9</v>
+        <v>17.9</v>
       </c>
       <c r="E53" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F53" t="n">
-        <v>4300</v>
+        <v>3450</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1941,20 +1953,20 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D54" t="n">
-        <v>17.9</v>
+        <v>19.5</v>
       </c>
       <c r="E54" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F54" t="n">
-        <v>3450</v>
+        <v>4050</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1970,20 +1982,20 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>42</v>
+        <v>34.5</v>
       </c>
       <c r="D55" t="n">
-        <v>19.5</v>
+        <v>18.1</v>
       </c>
       <c r="E55" t="n">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="F55" t="n">
-        <v>4050</v>
+        <v>2900</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1999,20 +2011,20 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>34.5</v>
+        <v>41.4</v>
       </c>
       <c r="D56" t="n">
-        <v>18.1</v>
+        <v>18.6</v>
       </c>
       <c r="E56" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F56" t="n">
-        <v>2900</v>
+        <v>3700</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2028,20 +2040,20 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>41.4</v>
+        <v>39</v>
       </c>
       <c r="D57" t="n">
-        <v>18.6</v>
+        <v>17.5</v>
       </c>
       <c r="E57" t="n">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="F57" t="n">
-        <v>3700</v>
+        <v>3550</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -2057,20 +2069,20 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>39</v>
+        <v>40.6</v>
       </c>
       <c r="D58" t="n">
-        <v>17.5</v>
+        <v>18.8</v>
       </c>
       <c r="E58" t="n">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="F58" t="n">
-        <v>3550</v>
+        <v>3800</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2086,20 +2098,20 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>40.6</v>
+        <v>36.5</v>
       </c>
       <c r="D59" t="n">
-        <v>18.8</v>
+        <v>16.6</v>
       </c>
       <c r="E59" t="n">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="F59" t="n">
-        <v>3800</v>
+        <v>2850</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -2115,20 +2127,20 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>36.5</v>
+        <v>37.6</v>
       </c>
       <c r="D60" t="n">
-        <v>16.6</v>
+        <v>19.1</v>
       </c>
       <c r="E60" t="n">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="F60" t="n">
-        <v>2850</v>
+        <v>3750</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2144,20 +2156,20 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>37.6</v>
+        <v>35.7</v>
       </c>
       <c r="D61" t="n">
-        <v>19.1</v>
+        <v>16.9</v>
       </c>
       <c r="E61" t="n">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F61" t="n">
-        <v>3750</v>
+        <v>3150</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -2173,20 +2185,20 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>35.7</v>
+        <v>41.3</v>
       </c>
       <c r="D62" t="n">
-        <v>16.9</v>
+        <v>21.1</v>
       </c>
       <c r="E62" t="n">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="F62" t="n">
-        <v>3150</v>
+        <v>4400</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2202,20 +2214,20 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>41.3</v>
+        <v>37.6</v>
       </c>
       <c r="D63" t="n">
-        <v>21.1</v>
+        <v>17</v>
       </c>
       <c r="E63" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="F63" t="n">
-        <v>4400</v>
+        <v>3600</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -2231,20 +2243,20 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>37.6</v>
+        <v>41.1</v>
       </c>
       <c r="D64" t="n">
-        <v>17</v>
+        <v>18.2</v>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F64" t="n">
-        <v>3600</v>
+        <v>4050</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2260,20 +2272,20 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>41.1</v>
+        <v>36.4</v>
       </c>
       <c r="D65" t="n">
-        <v>18.2</v>
+        <v>17.1</v>
       </c>
       <c r="E65" t="n">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F65" t="n">
-        <v>4050</v>
+        <v>2850</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -2289,20 +2301,20 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>36.4</v>
+        <v>41.6</v>
       </c>
       <c r="D66" t="n">
-        <v>17.1</v>
+        <v>18</v>
       </c>
       <c r="E66" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="F66" t="n">
-        <v>2850</v>
+        <v>3950</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2318,20 +2330,20 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>41.6</v>
+        <v>35.5</v>
       </c>
       <c r="D67" t="n">
-        <v>18</v>
+        <v>16.2</v>
       </c>
       <c r="E67" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F67" t="n">
-        <v>3950</v>
+        <v>3350</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -2347,20 +2359,20 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>35.5</v>
+        <v>41.1</v>
       </c>
       <c r="D68" t="n">
-        <v>16.2</v>
+        <v>19.1</v>
       </c>
       <c r="E68" t="n">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F68" t="n">
-        <v>3350</v>
+        <v>4100</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2372,24 +2384,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>41.1</v>
+        <v>35.9</v>
       </c>
       <c r="D69" t="n">
-        <v>19.1</v>
+        <v>16.6</v>
       </c>
       <c r="E69" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F69" t="n">
-        <v>4100</v>
+        <v>3050</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -2405,20 +2417,20 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>35.9</v>
+        <v>41.8</v>
       </c>
       <c r="D70" t="n">
-        <v>16.6</v>
+        <v>19.4</v>
       </c>
       <c r="E70" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="F70" t="n">
-        <v>3050</v>
+        <v>4450</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2434,20 +2446,20 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>41.8</v>
+        <v>33.5</v>
       </c>
       <c r="D71" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="E71" t="n">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="F71" t="n">
-        <v>4450</v>
+        <v>3600</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -2463,20 +2475,20 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>33.5</v>
+        <v>39.7</v>
       </c>
       <c r="D72" t="n">
-        <v>19</v>
+        <v>18.4</v>
       </c>
       <c r="E72" t="n">
         <v>190</v>
       </c>
       <c r="F72" t="n">
-        <v>3600</v>
+        <v>3900</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2492,20 +2504,20 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="D73" t="n">
-        <v>18.4</v>
+        <v>17.2</v>
       </c>
       <c r="E73" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F73" t="n">
-        <v>3900</v>
+        <v>3550</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -2521,20 +2533,20 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>39.6</v>
+        <v>45.8</v>
       </c>
       <c r="D74" t="n">
-        <v>17.2</v>
+        <v>18.9</v>
       </c>
       <c r="E74" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F74" t="n">
-        <v>3550</v>
+        <v>4150</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2550,20 +2562,20 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>45.8</v>
+        <v>35.5</v>
       </c>
       <c r="D75" t="n">
-        <v>18.9</v>
+        <v>17.5</v>
       </c>
       <c r="E75" t="n">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F75" t="n">
-        <v>4150</v>
+        <v>3700</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -2579,20 +2591,20 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>35.5</v>
+        <v>42.8</v>
       </c>
       <c r="D76" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="E76" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F76" t="n">
-        <v>3700</v>
+        <v>4250</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2608,20 +2620,20 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>42.8</v>
+        <v>40.9</v>
       </c>
       <c r="D77" t="n">
-        <v>18.5</v>
+        <v>16.8</v>
       </c>
       <c r="E77" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F77" t="n">
-        <v>4250</v>
+        <v>3700</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -2637,20 +2649,20 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>40.9</v>
+        <v>37.2</v>
       </c>
       <c r="D78" t="n">
-        <v>16.8</v>
+        <v>19.4</v>
       </c>
       <c r="E78" t="n">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F78" t="n">
-        <v>3700</v>
+        <v>3900</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2666,20 +2678,20 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>37.2</v>
+        <v>36.2</v>
       </c>
       <c r="D79" t="n">
-        <v>19.4</v>
+        <v>16.1</v>
       </c>
       <c r="E79" t="n">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F79" t="n">
-        <v>3900</v>
+        <v>3550</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -2695,20 +2707,20 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>36.2</v>
+        <v>42.1</v>
       </c>
       <c r="D80" t="n">
-        <v>16.1</v>
+        <v>19.1</v>
       </c>
       <c r="E80" t="n">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="F80" t="n">
-        <v>3550</v>
+        <v>4000</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2724,20 +2736,20 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>42.1</v>
+        <v>34.6</v>
       </c>
       <c r="D81" t="n">
-        <v>19.1</v>
+        <v>17.2</v>
       </c>
       <c r="E81" t="n">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="F81" t="n">
-        <v>4000</v>
+        <v>3200</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -2753,20 +2765,20 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>34.6</v>
+        <v>42.9</v>
       </c>
       <c r="D82" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="E82" t="n">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="F82" t="n">
-        <v>3200</v>
+        <v>4700</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2782,20 +2794,20 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>42.9</v>
+        <v>36.7</v>
       </c>
       <c r="D83" t="n">
-        <v>17.6</v>
+        <v>18.8</v>
       </c>
       <c r="E83" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F83" t="n">
-        <v>4700</v>
+        <v>3800</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -2811,20 +2823,20 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>36.7</v>
+        <v>35.1</v>
       </c>
       <c r="D84" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E84" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F84" t="n">
-        <v>3800</v>
+        <v>4200</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2836,24 +2848,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>35.1</v>
+        <v>37.3</v>
       </c>
       <c r="D85" t="n">
-        <v>19.4</v>
+        <v>17.8</v>
       </c>
       <c r="E85" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F85" t="n">
-        <v>4200</v>
+        <v>3350</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -2869,20 +2881,20 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>37.3</v>
+        <v>41.3</v>
       </c>
       <c r="D86" t="n">
-        <v>17.8</v>
+        <v>20.3</v>
       </c>
       <c r="E86" t="n">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F86" t="n">
-        <v>3350</v>
+        <v>3550</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2898,16 +2910,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>41.3</v>
+        <v>36.3</v>
       </c>
       <c r="D87" t="n">
-        <v>20.3</v>
+        <v>19.5</v>
       </c>
       <c r="E87" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F87" t="n">
-        <v>3550</v>
+        <v>3800</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -2927,20 +2939,20 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>36.3</v>
+        <v>36.9</v>
       </c>
       <c r="D88" t="n">
-        <v>19.5</v>
+        <v>18.6</v>
       </c>
       <c r="E88" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F88" t="n">
-        <v>3800</v>
+        <v>3500</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -2956,20 +2968,20 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>36.9</v>
+        <v>38.3</v>
       </c>
       <c r="D89" t="n">
-        <v>18.6</v>
+        <v>19.2</v>
       </c>
       <c r="E89" t="n">
         <v>189</v>
       </c>
       <c r="F89" t="n">
-        <v>3500</v>
+        <v>3950</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2985,20 +2997,20 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>38.3</v>
+        <v>38.9</v>
       </c>
       <c r="D90" t="n">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="E90" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F90" t="n">
-        <v>3950</v>
+        <v>3600</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -3014,16 +3026,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>38.9</v>
+        <v>35.7</v>
       </c>
       <c r="D91" t="n">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="E91" t="n">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="F91" t="n">
-        <v>3600</v>
+        <v>3550</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3043,20 +3055,20 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>35.7</v>
+        <v>41.1</v>
       </c>
       <c r="D92" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="E92" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="F92" t="n">
-        <v>3550</v>
+        <v>4300</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3072,20 +3084,20 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>41.1</v>
+        <v>34</v>
       </c>
       <c r="D93" t="n">
-        <v>18.1</v>
+        <v>17.1</v>
       </c>
       <c r="E93" t="n">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="F93" t="n">
-        <v>4300</v>
+        <v>3400</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -3101,20 +3113,20 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>34</v>
+        <v>39.6</v>
       </c>
       <c r="D94" t="n">
-        <v>17.1</v>
+        <v>18.1</v>
       </c>
       <c r="E94" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F94" t="n">
-        <v>3400</v>
+        <v>4450</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3130,20 +3142,20 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>39.6</v>
+        <v>36.2</v>
       </c>
       <c r="D95" t="n">
-        <v>18.1</v>
+        <v>17.3</v>
       </c>
       <c r="E95" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F95" t="n">
-        <v>4450</v>
+        <v>3300</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -3159,20 +3171,20 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>36.2</v>
+        <v>40.8</v>
       </c>
       <c r="D96" t="n">
-        <v>17.3</v>
+        <v>18.9</v>
       </c>
       <c r="E96" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="F96" t="n">
-        <v>3300</v>
+        <v>4300</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3188,20 +3200,20 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>40.8</v>
+        <v>38.1</v>
       </c>
       <c r="D97" t="n">
-        <v>18.9</v>
+        <v>18.6</v>
       </c>
       <c r="E97" t="n">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="F97" t="n">
-        <v>4300</v>
+        <v>3700</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -3217,20 +3229,20 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>38.1</v>
+        <v>40.3</v>
       </c>
       <c r="D98" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="E98" t="n">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F98" t="n">
-        <v>3700</v>
+        <v>4350</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3246,20 +3258,20 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>40.3</v>
+        <v>33.1</v>
       </c>
       <c r="D99" t="n">
-        <v>18.5</v>
+        <v>16.1</v>
       </c>
       <c r="E99" t="n">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="F99" t="n">
-        <v>4350</v>
+        <v>2900</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -3275,20 +3287,20 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>33.1</v>
+        <v>43.2</v>
       </c>
       <c r="D100" t="n">
-        <v>16.1</v>
+        <v>18.5</v>
       </c>
       <c r="E100" t="n">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="F100" t="n">
-        <v>2900</v>
+        <v>4100</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3300,24 +3312,24 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>43.2</v>
+        <v>35</v>
       </c>
       <c r="D101" t="n">
-        <v>18.5</v>
+        <v>17.9</v>
       </c>
       <c r="E101" t="n">
         <v>192</v>
       </c>
       <c r="F101" t="n">
-        <v>4100</v>
+        <v>3725</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -3333,20 +3345,20 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D102" t="n">
-        <v>17.9</v>
+        <v>20</v>
       </c>
       <c r="E102" t="n">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="F102" t="n">
-        <v>3725</v>
+        <v>4725</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3362,20 +3374,20 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>41</v>
+        <v>37.7</v>
       </c>
       <c r="D103" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E103" t="n">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="F103" t="n">
-        <v>4725</v>
+        <v>3075</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -3391,20 +3403,20 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>37.7</v>
+        <v>37.8</v>
       </c>
       <c r="D104" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E104" t="n">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="F104" t="n">
-        <v>3075</v>
+        <v>4250</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3420,20 +3432,20 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>37.8</v>
+        <v>37.9</v>
       </c>
       <c r="D105" t="n">
-        <v>20</v>
+        <v>18.6</v>
       </c>
       <c r="E105" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F105" t="n">
-        <v>4250</v>
+        <v>2925</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -3449,20 +3461,20 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>37.9</v>
+        <v>39.7</v>
       </c>
       <c r="D106" t="n">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
       <c r="E106" t="n">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F106" t="n">
-        <v>2925</v>
+        <v>3550</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3478,20 +3490,20 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>39.7</v>
+        <v>38.6</v>
       </c>
       <c r="D107" t="n">
-        <v>18.9</v>
+        <v>17.2</v>
       </c>
       <c r="E107" t="n">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="F107" t="n">
-        <v>3550</v>
+        <v>3750</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -3507,20 +3519,20 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>38.6</v>
+        <v>38.2</v>
       </c>
       <c r="D108" t="n">
-        <v>17.2</v>
+        <v>20</v>
       </c>
       <c r="E108" t="n">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="F108" t="n">
-        <v>3750</v>
+        <v>3900</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3536,20 +3548,20 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="D109" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E109" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="F109" t="n">
-        <v>3900</v>
+        <v>3175</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -3565,20 +3577,20 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>38.1</v>
+        <v>43.2</v>
       </c>
       <c r="D110" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E110" t="n">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="F110" t="n">
-        <v>3175</v>
+        <v>4775</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3594,20 +3606,20 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>43.2</v>
+        <v>38.1</v>
       </c>
       <c r="D111" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="E111" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F111" t="n">
-        <v>4775</v>
+        <v>3825</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -3623,20 +3635,20 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>38.1</v>
+        <v>45.6</v>
       </c>
       <c r="D112" t="n">
-        <v>16.5</v>
+        <v>20.3</v>
       </c>
       <c r="E112" t="n">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F112" t="n">
-        <v>3825</v>
+        <v>4600</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3652,20 +3664,20 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>45.6</v>
+        <v>39.7</v>
       </c>
       <c r="D113" t="n">
-        <v>20.3</v>
+        <v>17.7</v>
       </c>
       <c r="E113" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F113" t="n">
-        <v>4600</v>
+        <v>3200</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -3681,20 +3693,20 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>39.7</v>
+        <v>42.2</v>
       </c>
       <c r="D114" t="n">
-        <v>17.7</v>
+        <v>19.5</v>
       </c>
       <c r="E114" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F114" t="n">
-        <v>3200</v>
+        <v>4275</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3710,20 +3722,20 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>42.2</v>
+        <v>39.6</v>
       </c>
       <c r="D115" t="n">
-        <v>19.5</v>
+        <v>20.7</v>
       </c>
       <c r="E115" t="n">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F115" t="n">
-        <v>4275</v>
+        <v>3900</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -3739,20 +3751,20 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>39.6</v>
+        <v>42.7</v>
       </c>
       <c r="D116" t="n">
-        <v>20.7</v>
+        <v>18.3</v>
       </c>
       <c r="E116" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="F116" t="n">
-        <v>3900</v>
+        <v>4075</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3764,24 +3776,24 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>42.7</v>
+        <v>38.6</v>
       </c>
       <c r="D117" t="n">
-        <v>18.3</v>
+        <v>17</v>
       </c>
       <c r="E117" t="n">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="F117" t="n">
-        <v>4075</v>
+        <v>2900</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -3797,20 +3809,20 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>38.6</v>
+        <v>37.3</v>
       </c>
       <c r="D118" t="n">
-        <v>17</v>
+        <v>20.5</v>
       </c>
       <c r="E118" t="n">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="F118" t="n">
-        <v>2900</v>
+        <v>3775</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3826,20 +3838,20 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>37.3</v>
+        <v>35.7</v>
       </c>
       <c r="D119" t="n">
-        <v>20.5</v>
+        <v>17</v>
       </c>
       <c r="E119" t="n">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="F119" t="n">
-        <v>3775</v>
+        <v>3350</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -3855,20 +3867,20 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>35.7</v>
+        <v>41.1</v>
       </c>
       <c r="D120" t="n">
-        <v>17</v>
+        <v>18.6</v>
       </c>
       <c r="E120" t="n">
         <v>189</v>
       </c>
       <c r="F120" t="n">
-        <v>3350</v>
+        <v>3325</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3884,20 +3896,20 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>41.1</v>
+        <v>36.2</v>
       </c>
       <c r="D121" t="n">
-        <v>18.6</v>
+        <v>17.2</v>
       </c>
       <c r="E121" t="n">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F121" t="n">
-        <v>3325</v>
+        <v>3150</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -3913,20 +3925,20 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>36.2</v>
+        <v>37.7</v>
       </c>
       <c r="D122" t="n">
-        <v>17.2</v>
+        <v>19.8</v>
       </c>
       <c r="E122" t="n">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="F122" t="n">
-        <v>3150</v>
+        <v>3500</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3942,20 +3954,20 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>37.7</v>
+        <v>40.2</v>
       </c>
       <c r="D123" t="n">
-        <v>19.8</v>
+        <v>17</v>
       </c>
       <c r="E123" t="n">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="F123" t="n">
-        <v>3500</v>
+        <v>3450</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -3971,20 +3983,20 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>40.2</v>
+        <v>41.4</v>
       </c>
       <c r="D124" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="E124" t="n">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="F124" t="n">
-        <v>3450</v>
+        <v>3875</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4000,20 +4012,20 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>41.4</v>
+        <v>35.2</v>
       </c>
       <c r="D125" t="n">
-        <v>18.5</v>
+        <v>15.9</v>
       </c>
       <c r="E125" t="n">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="F125" t="n">
-        <v>3875</v>
+        <v>3050</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -4029,20 +4041,20 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>35.2</v>
+        <v>40.6</v>
       </c>
       <c r="D126" t="n">
-        <v>15.9</v>
+        <v>19</v>
       </c>
       <c r="E126" t="n">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="F126" t="n">
-        <v>3050</v>
+        <v>4000</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4058,20 +4070,20 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>40.6</v>
+        <v>38.8</v>
       </c>
       <c r="D127" t="n">
-        <v>19</v>
+        <v>17.6</v>
       </c>
       <c r="E127" t="n">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="F127" t="n">
-        <v>4000</v>
+        <v>3275</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -4087,20 +4099,20 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>38.8</v>
+        <v>41.5</v>
       </c>
       <c r="D128" t="n">
-        <v>17.6</v>
+        <v>18.3</v>
       </c>
       <c r="E128" t="n">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F128" t="n">
-        <v>3275</v>
+        <v>4300</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4116,20 +4128,20 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>41.5</v>
+        <v>39</v>
       </c>
       <c r="D129" t="n">
-        <v>18.3</v>
+        <v>17.1</v>
       </c>
       <c r="E129" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F129" t="n">
-        <v>4300</v>
+        <v>3050</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -4145,20 +4157,20 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>39</v>
+        <v>44.1</v>
       </c>
       <c r="D130" t="n">
-        <v>17.1</v>
+        <v>18</v>
       </c>
       <c r="E130" t="n">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="F130" t="n">
-        <v>3050</v>
+        <v>4000</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4174,20 +4186,20 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>44.1</v>
+        <v>38.5</v>
       </c>
       <c r="D131" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="E131" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="F131" t="n">
-        <v>4000</v>
+        <v>3325</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -4203,20 +4215,20 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>38.5</v>
+        <v>43.1</v>
       </c>
       <c r="D132" t="n">
-        <v>17.9</v>
+        <v>19.2</v>
       </c>
       <c r="E132" t="n">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="F132" t="n">
-        <v>3325</v>
+        <v>3500</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4228,24 +4240,24 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>43.1</v>
+        <v>36.8</v>
       </c>
       <c r="D133" t="n">
-        <v>19.2</v>
+        <v>18.5</v>
       </c>
       <c r="E133" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F133" t="n">
         <v>3500</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -4261,20 +4273,20 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>36.8</v>
+        <v>37.5</v>
       </c>
       <c r="D134" t="n">
         <v>18.5</v>
       </c>
       <c r="E134" t="n">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F134" t="n">
-        <v>3500</v>
+        <v>4475</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4290,20 +4302,20 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>37.5</v>
+        <v>38.1</v>
       </c>
       <c r="D135" t="n">
-        <v>18.5</v>
+        <v>17.6</v>
       </c>
       <c r="E135" t="n">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="F135" t="n">
-        <v>4475</v>
+        <v>3425</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -4319,20 +4331,20 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>38.1</v>
+        <v>41.1</v>
       </c>
       <c r="D136" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="E136" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F136" t="n">
-        <v>3425</v>
+        <v>3900</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4348,20 +4360,20 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>41.1</v>
+        <v>35.6</v>
       </c>
       <c r="D137" t="n">
         <v>17.5</v>
       </c>
       <c r="E137" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F137" t="n">
-        <v>3900</v>
+        <v>3175</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -4377,20 +4389,20 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>35.6</v>
+        <v>40.2</v>
       </c>
       <c r="D138" t="n">
-        <v>17.5</v>
+        <v>20.1</v>
       </c>
       <c r="E138" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F138" t="n">
-        <v>3175</v>
+        <v>3975</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4406,20 +4418,20 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>40.2</v>
+        <v>37</v>
       </c>
       <c r="D139" t="n">
-        <v>20.1</v>
+        <v>16.5</v>
       </c>
       <c r="E139" t="n">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="F139" t="n">
-        <v>3975</v>
+        <v>3400</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -4435,20 +4447,20 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>37</v>
+        <v>39.7</v>
       </c>
       <c r="D140" t="n">
-        <v>16.5</v>
+        <v>17.9</v>
       </c>
       <c r="E140" t="n">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F140" t="n">
-        <v>3400</v>
+        <v>4250</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4464,20 +4476,20 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>39.7</v>
+        <v>40.2</v>
       </c>
       <c r="D141" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="E141" t="n">
         <v>193</v>
       </c>
       <c r="F141" t="n">
-        <v>4250</v>
+        <v>3400</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -4493,20 +4505,20 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>40.2</v>
+        <v>40.6</v>
       </c>
       <c r="D142" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="E142" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F142" t="n">
-        <v>3400</v>
+        <v>3475</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4522,20 +4534,20 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>40.6</v>
+        <v>32.1</v>
       </c>
       <c r="D143" t="n">
-        <v>17.2</v>
+        <v>15.5</v>
       </c>
       <c r="E143" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F143" t="n">
-        <v>3475</v>
+        <v>3050</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -4551,20 +4563,20 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>32.1</v>
+        <v>40.7</v>
       </c>
       <c r="D144" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="E144" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F144" t="n">
-        <v>3050</v>
+        <v>3725</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4580,20 +4592,20 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>40.7</v>
+        <v>37.3</v>
       </c>
       <c r="D145" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="E145" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F145" t="n">
-        <v>3725</v>
+        <v>3000</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -4609,20 +4621,20 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>37.3</v>
+        <v>39</v>
       </c>
       <c r="D146" t="n">
-        <v>16.8</v>
+        <v>18.7</v>
       </c>
       <c r="E146" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="F146" t="n">
-        <v>3000</v>
+        <v>3650</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4638,16 +4650,16 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>39</v>
+        <v>39.2</v>
       </c>
       <c r="D147" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="E147" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F147" t="n">
-        <v>3650</v>
+        <v>4250</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -4667,20 +4679,20 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>39.2</v>
+        <v>36.6</v>
       </c>
       <c r="D148" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="E148" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F148" t="n">
-        <v>4250</v>
+        <v>3475</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -4696,16 +4708,16 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>36.6</v>
+        <v>36</v>
       </c>
       <c r="D149" t="n">
-        <v>18.4</v>
+        <v>17.8</v>
       </c>
       <c r="E149" t="n">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="F149" t="n">
-        <v>3475</v>
+        <v>3450</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -4725,20 +4737,20 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>36</v>
+        <v>37.8</v>
       </c>
       <c r="D150" t="n">
-        <v>17.8</v>
+        <v>18.1</v>
       </c>
       <c r="E150" t="n">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F150" t="n">
-        <v>3450</v>
+        <v>3750</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4754,20 +4766,20 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>37.8</v>
+        <v>36</v>
       </c>
       <c r="D151" t="n">
-        <v>18.1</v>
+        <v>17.1</v>
       </c>
       <c r="E151" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F151" t="n">
-        <v>3750</v>
+        <v>3700</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -4783,27 +4795,27 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>36</v>
+        <v>41.5</v>
       </c>
       <c r="D152" t="n">
-        <v>17.1</v>
+        <v>18.5</v>
       </c>
       <c r="E152" t="n">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="F152" t="n">
-        <v>3700</v>
+        <v>4000</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Adelie</t>
+          <t>Chinstrap</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4812,20 +4824,20 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>41.5</v>
+        <v>46.5</v>
       </c>
       <c r="D153" t="n">
-        <v>18.5</v>
+        <v>17.9</v>
       </c>
       <c r="E153" t="n">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="F153" t="n">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -4841,20 +4853,20 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>46.5</v>
+        <v>50</v>
       </c>
       <c r="D154" t="n">
-        <v>17.9</v>
+        <v>19.5</v>
       </c>
       <c r="E154" t="n">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F154" t="n">
-        <v>3500</v>
+        <v>3900</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4870,16 +4882,16 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>50</v>
+        <v>51.3</v>
       </c>
       <c r="D155" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="E155" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F155" t="n">
-        <v>3900</v>
+        <v>3650</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -4899,20 +4911,20 @@
         </is>
       </c>
       <c r="C156" t="n">
-        <v>51.3</v>
+        <v>45.4</v>
       </c>
       <c r="D156" t="n">
-        <v>19.2</v>
+        <v>18.7</v>
       </c>
       <c r="E156" t="n">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F156" t="n">
-        <v>3650</v>
+        <v>3525</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -4928,20 +4940,20 @@
         </is>
       </c>
       <c r="C157" t="n">
-        <v>45.4</v>
+        <v>52.7</v>
       </c>
       <c r="D157" t="n">
-        <v>18.7</v>
+        <v>19.8</v>
       </c>
       <c r="E157" t="n">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="F157" t="n">
-        <v>3525</v>
+        <v>3725</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4957,20 +4969,20 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>52.7</v>
+        <v>45.2</v>
       </c>
       <c r="D158" t="n">
-        <v>19.8</v>
+        <v>17.8</v>
       </c>
       <c r="E158" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F158" t="n">
-        <v>3725</v>
+        <v>3950</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -4986,16 +4998,16 @@
         </is>
       </c>
       <c r="C159" t="n">
-        <v>45.2</v>
+        <v>46.1</v>
       </c>
       <c r="D159" t="n">
-        <v>17.8</v>
+        <v>18.2</v>
       </c>
       <c r="E159" t="n">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="F159" t="n">
-        <v>3950</v>
+        <v>3250</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -5015,20 +5027,20 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>46.1</v>
+        <v>51.3</v>
       </c>
       <c r="D160" t="n">
         <v>18.2</v>
       </c>
       <c r="E160" t="n">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="F160" t="n">
-        <v>3250</v>
+        <v>3750</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5044,20 +5056,20 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>51.3</v>
+        <v>46</v>
       </c>
       <c r="D161" t="n">
-        <v>18.2</v>
+        <v>18.9</v>
       </c>
       <c r="E161" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F161" t="n">
-        <v>3750</v>
+        <v>4150</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -5073,20 +5085,20 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>46</v>
+        <v>51.3</v>
       </c>
       <c r="D162" t="n">
-        <v>18.9</v>
+        <v>19.9</v>
       </c>
       <c r="E162" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F162" t="n">
-        <v>4150</v>
+        <v>3700</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5102,20 +5114,20 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>51.3</v>
+        <v>46.6</v>
       </c>
       <c r="D163" t="n">
-        <v>19.9</v>
+        <v>17.8</v>
       </c>
       <c r="E163" t="n">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F163" t="n">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -5131,20 +5143,20 @@
         </is>
       </c>
       <c r="C164" t="n">
-        <v>46.6</v>
+        <v>51.7</v>
       </c>
       <c r="D164" t="n">
-        <v>17.8</v>
+        <v>20.3</v>
       </c>
       <c r="E164" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F164" t="n">
-        <v>3800</v>
+        <v>3775</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5160,20 +5172,20 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>51.7</v>
+        <v>47</v>
       </c>
       <c r="D165" t="n">
-        <v>20.3</v>
+        <v>17.3</v>
       </c>
       <c r="E165" t="n">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F165" t="n">
-        <v>3775</v>
+        <v>3700</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -5189,20 +5201,20 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D166" t="n">
-        <v>17.3</v>
+        <v>18.1</v>
       </c>
       <c r="E166" t="n">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="F166" t="n">
-        <v>3700</v>
+        <v>4050</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5218,20 +5230,20 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>52</v>
+        <v>45.9</v>
       </c>
       <c r="D167" t="n">
-        <v>18.1</v>
+        <v>17.1</v>
       </c>
       <c r="E167" t="n">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F167" t="n">
-        <v>4050</v>
+        <v>3575</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -5247,20 +5259,20 @@
         </is>
       </c>
       <c r="C168" t="n">
-        <v>45.9</v>
+        <v>50.5</v>
       </c>
       <c r="D168" t="n">
-        <v>17.1</v>
+        <v>19.6</v>
       </c>
       <c r="E168" t="n">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="F168" t="n">
-        <v>3575</v>
+        <v>4050</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5276,16 +5288,16 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>50.5</v>
+        <v>50.3</v>
       </c>
       <c r="D169" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="E169" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F169" t="n">
-        <v>4050</v>
+        <v>3300</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -5305,20 +5317,20 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>50.3</v>
+        <v>58</v>
       </c>
       <c r="D170" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E170" t="n">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="F170" t="n">
-        <v>3300</v>
+        <v>3700</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -5334,16 +5346,16 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>58</v>
+        <v>46.4</v>
       </c>
       <c r="D171" t="n">
-        <v>17.8</v>
+        <v>18.6</v>
       </c>
       <c r="E171" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="F171" t="n">
-        <v>3700</v>
+        <v>3450</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -5363,20 +5375,20 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>46.4</v>
+        <v>49.2</v>
       </c>
       <c r="D172" t="n">
-        <v>18.6</v>
+        <v>18.2</v>
       </c>
       <c r="E172" t="n">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F172" t="n">
-        <v>3450</v>
+        <v>4400</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5392,20 +5404,20 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>49.2</v>
+        <v>42.4</v>
       </c>
       <c r="D173" t="n">
-        <v>18.2</v>
+        <v>17.3</v>
       </c>
       <c r="E173" t="n">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="F173" t="n">
-        <v>4400</v>
+        <v>3600</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -5421,20 +5433,20 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>42.4</v>
+        <v>48.5</v>
       </c>
       <c r="D174" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="E174" t="n">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="F174" t="n">
-        <v>3600</v>
+        <v>3400</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5450,20 +5462,20 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>48.5</v>
+        <v>43.2</v>
       </c>
       <c r="D175" t="n">
-        <v>17.5</v>
+        <v>16.6</v>
       </c>
       <c r="E175" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F175" t="n">
-        <v>3400</v>
+        <v>2900</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -5479,20 +5491,20 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>43.2</v>
+        <v>50.6</v>
       </c>
       <c r="D176" t="n">
-        <v>16.6</v>
+        <v>19.4</v>
       </c>
       <c r="E176" t="n">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F176" t="n">
-        <v>2900</v>
+        <v>3800</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5508,20 +5520,20 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>50.6</v>
+        <v>46.7</v>
       </c>
       <c r="D177" t="n">
-        <v>19.4</v>
+        <v>17.9</v>
       </c>
       <c r="E177" t="n">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F177" t="n">
-        <v>3800</v>
+        <v>3300</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -5537,20 +5549,20 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>46.7</v>
+        <v>52</v>
       </c>
       <c r="D178" t="n">
-        <v>17.9</v>
+        <v>19</v>
       </c>
       <c r="E178" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F178" t="n">
-        <v>3300</v>
+        <v>4150</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5566,20 +5578,20 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>52</v>
+        <v>50.5</v>
       </c>
       <c r="D179" t="n">
-        <v>19</v>
+        <v>18.4</v>
       </c>
       <c r="E179" t="n">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F179" t="n">
-        <v>4150</v>
+        <v>3400</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -5595,20 +5607,20 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>50.5</v>
+        <v>49.5</v>
       </c>
       <c r="D180" t="n">
-        <v>18.4</v>
+        <v>19</v>
       </c>
       <c r="E180" t="n">
         <v>200</v>
       </c>
       <c r="F180" t="n">
-        <v>3400</v>
+        <v>3800</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5624,20 +5636,20 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>49.5</v>
+        <v>46.4</v>
       </c>
       <c r="D181" t="n">
-        <v>19</v>
+        <v>17.8</v>
       </c>
       <c r="E181" t="n">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="F181" t="n">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -5653,20 +5665,20 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>46.4</v>
+        <v>52.8</v>
       </c>
       <c r="D182" t="n">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E182" t="n">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="F182" t="n">
-        <v>3700</v>
+        <v>4550</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5682,20 +5694,20 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>52.8</v>
+        <v>40.9</v>
       </c>
       <c r="D183" t="n">
-        <v>20</v>
+        <v>16.6</v>
       </c>
       <c r="E183" t="n">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="F183" t="n">
-        <v>4550</v>
+        <v>3200</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -5711,20 +5723,20 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>40.9</v>
+        <v>54.2</v>
       </c>
       <c r="D184" t="n">
-        <v>16.6</v>
+        <v>20.8</v>
       </c>
       <c r="E184" t="n">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="F184" t="n">
-        <v>3200</v>
+        <v>4300</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5740,20 +5752,20 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>54.2</v>
+        <v>42.5</v>
       </c>
       <c r="D185" t="n">
-        <v>20.8</v>
+        <v>16.7</v>
       </c>
       <c r="E185" t="n">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="F185" t="n">
-        <v>4300</v>
+        <v>3350</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -5769,20 +5781,20 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>42.5</v>
+        <v>51</v>
       </c>
       <c r="D186" t="n">
-        <v>16.7</v>
+        <v>18.8</v>
       </c>
       <c r="E186" t="n">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="F186" t="n">
-        <v>3350</v>
+        <v>4100</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5798,16 +5810,16 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>51</v>
+        <v>49.7</v>
       </c>
       <c r="D187" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="E187" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="F187" t="n">
-        <v>4100</v>
+        <v>3600</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -5827,20 +5839,20 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>49.7</v>
+        <v>47.5</v>
       </c>
       <c r="D188" t="n">
-        <v>18.6</v>
+        <v>16.8</v>
       </c>
       <c r="E188" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F188" t="n">
-        <v>3600</v>
+        <v>3900</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -5856,16 +5868,16 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>47.5</v>
+        <v>47.6</v>
       </c>
       <c r="D189" t="n">
-        <v>16.8</v>
+        <v>18.3</v>
       </c>
       <c r="E189" t="n">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F189" t="n">
-        <v>3900</v>
+        <v>3850</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -5885,20 +5897,20 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>47.6</v>
+        <v>52</v>
       </c>
       <c r="D190" t="n">
-        <v>18.3</v>
+        <v>20.7</v>
       </c>
       <c r="E190" t="n">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="F190" t="n">
-        <v>3850</v>
+        <v>4800</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5914,20 +5926,20 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>52</v>
+        <v>46.9</v>
       </c>
       <c r="D191" t="n">
-        <v>20.7</v>
+        <v>16.6</v>
       </c>
       <c r="E191" t="n">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="F191" t="n">
-        <v>4800</v>
+        <v>2700</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -5943,20 +5955,20 @@
         </is>
       </c>
       <c r="C192" t="n">
-        <v>46.9</v>
+        <v>53.5</v>
       </c>
       <c r="D192" t="n">
-        <v>16.6</v>
+        <v>19.9</v>
       </c>
       <c r="E192" t="n">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="F192" t="n">
-        <v>2700</v>
+        <v>4500</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5972,16 +5984,16 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>53.5</v>
+        <v>49</v>
       </c>
       <c r="D193" t="n">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="E193" t="n">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F193" t="n">
-        <v>4500</v>
+        <v>3950</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -6001,20 +6013,20 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>49</v>
+        <v>46.2</v>
       </c>
       <c r="D194" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="E194" t="n">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="F194" t="n">
-        <v>3950</v>
+        <v>3650</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -6030,20 +6042,20 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>46.2</v>
+        <v>50.9</v>
       </c>
       <c r="D195" t="n">
-        <v>17.5</v>
+        <v>19.1</v>
       </c>
       <c r="E195" t="n">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="F195" t="n">
-        <v>3650</v>
+        <v>3550</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6059,20 +6071,20 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>50.9</v>
+        <v>45.5</v>
       </c>
       <c r="D196" t="n">
-        <v>19.1</v>
+        <v>17</v>
       </c>
       <c r="E196" t="n">
         <v>196</v>
       </c>
       <c r="F196" t="n">
-        <v>3550</v>
+        <v>3500</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -6088,16 +6100,16 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>45.5</v>
+        <v>50.9</v>
       </c>
       <c r="D197" t="n">
-        <v>17</v>
+        <v>17.9</v>
       </c>
       <c r="E197" t="n">
         <v>196</v>
       </c>
       <c r="F197" t="n">
-        <v>3500</v>
+        <v>3675</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -6117,20 +6129,20 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>50.9</v>
+        <v>50.8</v>
       </c>
       <c r="D198" t="n">
-        <v>17.9</v>
+        <v>18.5</v>
       </c>
       <c r="E198" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F198" t="n">
-        <v>3675</v>
+        <v>4450</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6146,20 +6158,20 @@
         </is>
       </c>
       <c r="C199" t="n">
-        <v>50.8</v>
+        <v>50.1</v>
       </c>
       <c r="D199" t="n">
-        <v>18.5</v>
+        <v>17.9</v>
       </c>
       <c r="E199" t="n">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F199" t="n">
-        <v>4450</v>
+        <v>3400</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -6175,20 +6187,20 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>50.1</v>
+        <v>49</v>
       </c>
       <c r="D200" t="n">
-        <v>17.9</v>
+        <v>19.6</v>
       </c>
       <c r="E200" t="n">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="F200" t="n">
-        <v>3400</v>
+        <v>4300</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6204,16 +6216,16 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>49</v>
+        <v>51.5</v>
       </c>
       <c r="D201" t="n">
-        <v>19.6</v>
+        <v>18.7</v>
       </c>
       <c r="E201" t="n">
-        <v>212</v>
+        <v>187</v>
       </c>
       <c r="F201" t="n">
-        <v>4300</v>
+        <v>3250</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -6233,20 +6245,20 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>51.5</v>
+        <v>49.8</v>
       </c>
       <c r="D202" t="n">
-        <v>18.7</v>
+        <v>17.3</v>
       </c>
       <c r="E202" t="n">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="F202" t="n">
-        <v>3250</v>
+        <v>3675</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -6262,16 +6274,16 @@
         </is>
       </c>
       <c r="C203" t="n">
-        <v>49.8</v>
+        <v>48.1</v>
       </c>
       <c r="D203" t="n">
-        <v>17.3</v>
+        <v>16.4</v>
       </c>
       <c r="E203" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F203" t="n">
-        <v>3675</v>
+        <v>3325</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -6291,20 +6303,20 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>48.1</v>
+        <v>51.4</v>
       </c>
       <c r="D204" t="n">
-        <v>16.4</v>
+        <v>19</v>
       </c>
       <c r="E204" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F204" t="n">
-        <v>3325</v>
+        <v>3950</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6320,20 +6332,20 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>51.4</v>
+        <v>45.7</v>
       </c>
       <c r="D205" t="n">
-        <v>19</v>
+        <v>17.3</v>
       </c>
       <c r="E205" t="n">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="F205" t="n">
-        <v>3950</v>
+        <v>3600</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -6349,20 +6361,20 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>45.7</v>
+        <v>50.7</v>
       </c>
       <c r="D206" t="n">
-        <v>17.3</v>
+        <v>19.7</v>
       </c>
       <c r="E206" t="n">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="F206" t="n">
-        <v>3600</v>
+        <v>4050</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6378,20 +6390,20 @@
         </is>
       </c>
       <c r="C207" t="n">
-        <v>50.7</v>
+        <v>42.5</v>
       </c>
       <c r="D207" t="n">
-        <v>19.7</v>
+        <v>17.3</v>
       </c>
       <c r="E207" t="n">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="F207" t="n">
-        <v>4050</v>
+        <v>3350</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -6407,20 +6419,20 @@
         </is>
       </c>
       <c r="C208" t="n">
-        <v>42.5</v>
+        <v>52.2</v>
       </c>
       <c r="D208" t="n">
-        <v>17.3</v>
+        <v>18.8</v>
       </c>
       <c r="E208" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="F208" t="n">
-        <v>3350</v>
+        <v>3450</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6436,20 +6448,20 @@
         </is>
       </c>
       <c r="C209" t="n">
-        <v>52.2</v>
+        <v>45.2</v>
       </c>
       <c r="D209" t="n">
-        <v>18.8</v>
+        <v>16.6</v>
       </c>
       <c r="E209" t="n">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F209" t="n">
-        <v>3450</v>
+        <v>3250</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -6465,20 +6477,20 @@
         </is>
       </c>
       <c r="C210" t="n">
-        <v>45.2</v>
+        <v>49.3</v>
       </c>
       <c r="D210" t="n">
-        <v>16.6</v>
+        <v>19.9</v>
       </c>
       <c r="E210" t="n">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="F210" t="n">
-        <v>3250</v>
+        <v>4050</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6494,16 +6506,16 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>49.3</v>
+        <v>50.2</v>
       </c>
       <c r="D211" t="n">
-        <v>19.9</v>
+        <v>18.8</v>
       </c>
       <c r="E211" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F211" t="n">
-        <v>4050</v>
+        <v>3800</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -6523,20 +6535,20 @@
         </is>
       </c>
       <c r="C212" t="n">
-        <v>50.2</v>
+        <v>45.6</v>
       </c>
       <c r="D212" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E212" t="n">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="F212" t="n">
-        <v>3800</v>
+        <v>3525</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -6552,20 +6564,20 @@
         </is>
       </c>
       <c r="C213" t="n">
-        <v>45.6</v>
+        <v>51.9</v>
       </c>
       <c r="D213" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="E213" t="n">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="F213" t="n">
-        <v>3525</v>
+        <v>3950</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6581,20 +6593,20 @@
         </is>
       </c>
       <c r="C214" t="n">
-        <v>51.9</v>
+        <v>46.8</v>
       </c>
       <c r="D214" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="E214" t="n">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="F214" t="n">
-        <v>3950</v>
+        <v>3650</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -6610,13 +6622,13 @@
         </is>
       </c>
       <c r="C215" t="n">
-        <v>46.8</v>
+        <v>45.7</v>
       </c>
       <c r="D215" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="E215" t="n">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F215" t="n">
         <v>3650</v>
@@ -6639,20 +6651,20 @@
         </is>
       </c>
       <c r="C216" t="n">
-        <v>45.7</v>
+        <v>55.8</v>
       </c>
       <c r="D216" t="n">
-        <v>17</v>
+        <v>19.8</v>
       </c>
       <c r="E216" t="n">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="F216" t="n">
-        <v>3650</v>
+        <v>4000</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6668,20 +6680,20 @@
         </is>
       </c>
       <c r="C217" t="n">
-        <v>55.8</v>
+        <v>43.5</v>
       </c>
       <c r="D217" t="n">
-        <v>19.8</v>
+        <v>18.1</v>
       </c>
       <c r="E217" t="n">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="F217" t="n">
-        <v>4000</v>
+        <v>3400</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -6697,20 +6709,20 @@
         </is>
       </c>
       <c r="C218" t="n">
-        <v>43.5</v>
+        <v>49.6</v>
       </c>
       <c r="D218" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="E218" t="n">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="F218" t="n">
-        <v>3400</v>
+        <v>3775</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6726,16 +6738,16 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>49.6</v>
+        <v>50.8</v>
       </c>
       <c r="D219" t="n">
-        <v>18.2</v>
+        <v>19</v>
       </c>
       <c r="E219" t="n">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="F219" t="n">
-        <v>3775</v>
+        <v>4100</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -6755,45 +6767,45 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>50.8</v>
+        <v>50.2</v>
       </c>
       <c r="D220" t="n">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="E220" t="n">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="F220" t="n">
-        <v>4100</v>
+        <v>3775</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Chinstrap</t>
+          <t>Gentoo</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C221" t="n">
-        <v>50.2</v>
+        <v>46.1</v>
       </c>
       <c r="D221" t="n">
-        <v>18.7</v>
+        <v>13.2</v>
       </c>
       <c r="E221" t="n">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="F221" t="n">
-        <v>3775</v>
+        <v>4500</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -6813,20 +6825,20 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>46.1</v>
+        <v>50</v>
       </c>
       <c r="D222" t="n">
-        <v>13.2</v>
+        <v>16.3</v>
       </c>
       <c r="E222" t="n">
-        <v>211</v>
+        <v>230</v>
       </c>
       <c r="F222" t="n">
-        <v>4500</v>
+        <v>5700</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6842,20 +6854,20 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>50</v>
+        <v>48.7</v>
       </c>
       <c r="D223" t="n">
-        <v>16.3</v>
+        <v>14.1</v>
       </c>
       <c r="E223" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="F223" t="n">
-        <v>5700</v>
+        <v>4450</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -6871,20 +6883,20 @@
         </is>
       </c>
       <c r="C224" t="n">
-        <v>48.7</v>
+        <v>50</v>
       </c>
       <c r="D224" t="n">
-        <v>14.1</v>
+        <v>15.2</v>
       </c>
       <c r="E224" t="n">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="F224" t="n">
-        <v>4450</v>
+        <v>5700</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -6900,16 +6912,16 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>50</v>
+        <v>47.6</v>
       </c>
       <c r="D225" t="n">
-        <v>15.2</v>
+        <v>14.5</v>
       </c>
       <c r="E225" t="n">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F225" t="n">
-        <v>5700</v>
+        <v>5400</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -6929,20 +6941,20 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>47.6</v>
+        <v>46.5</v>
       </c>
       <c r="D226" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="E226" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F226" t="n">
-        <v>5400</v>
+        <v>4550</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -6958,16 +6970,16 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>46.5</v>
+        <v>45.4</v>
       </c>
       <c r="D227" t="n">
-        <v>13.5</v>
+        <v>14.6</v>
       </c>
       <c r="E227" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F227" t="n">
-        <v>4550</v>
+        <v>4800</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -6987,20 +6999,20 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>45.4</v>
+        <v>46.7</v>
       </c>
       <c r="D228" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E228" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="F228" t="n">
-        <v>4800</v>
+        <v>5200</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -7016,20 +7028,20 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>46.7</v>
+        <v>43.3</v>
       </c>
       <c r="D229" t="n">
-        <v>15.3</v>
+        <v>13.4</v>
       </c>
       <c r="E229" t="n">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="F229" t="n">
-        <v>5200</v>
+        <v>4400</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -7045,20 +7057,20 @@
         </is>
       </c>
       <c r="C230" t="n">
-        <v>43.3</v>
+        <v>46.8</v>
       </c>
       <c r="D230" t="n">
-        <v>13.4</v>
+        <v>15.4</v>
       </c>
       <c r="E230" t="n">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F230" t="n">
-        <v>4400</v>
+        <v>5150</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -7074,20 +7086,20 @@
         </is>
       </c>
       <c r="C231" t="n">
-        <v>46.8</v>
+        <v>40.9</v>
       </c>
       <c r="D231" t="n">
-        <v>15.4</v>
+        <v>13.7</v>
       </c>
       <c r="E231" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F231" t="n">
-        <v>5150</v>
+        <v>4650</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -7103,20 +7115,20 @@
         </is>
       </c>
       <c r="C232" t="n">
-        <v>40.9</v>
+        <v>49</v>
       </c>
       <c r="D232" t="n">
-        <v>13.7</v>
+        <v>16.1</v>
       </c>
       <c r="E232" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F232" t="n">
-        <v>4650</v>
+        <v>5550</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -7132,20 +7144,20 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>49</v>
+        <v>45.5</v>
       </c>
       <c r="D233" t="n">
-        <v>16.1</v>
+        <v>13.7</v>
       </c>
       <c r="E233" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F233" t="n">
-        <v>5550</v>
+        <v>4650</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -7161,20 +7173,20 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>45.5</v>
+        <v>48.4</v>
       </c>
       <c r="D234" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="E234" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F234" t="n">
-        <v>4650</v>
+        <v>5850</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -7190,20 +7202,20 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>48.4</v>
+        <v>45.8</v>
       </c>
       <c r="D235" t="n">
         <v>14.6</v>
       </c>
       <c r="E235" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F235" t="n">
-        <v>5850</v>
+        <v>4200</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -7219,20 +7231,20 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>45.8</v>
+        <v>49.3</v>
       </c>
       <c r="D236" t="n">
-        <v>14.6</v>
+        <v>15.7</v>
       </c>
       <c r="E236" t="n">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="F236" t="n">
-        <v>4200</v>
+        <v>5850</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -7248,20 +7260,20 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>49.3</v>
+        <v>42</v>
       </c>
       <c r="D237" t="n">
-        <v>15.7</v>
+        <v>13.5</v>
       </c>
       <c r="E237" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F237" t="n">
-        <v>5850</v>
+        <v>4150</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -7277,20 +7289,20 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>42</v>
+        <v>49.2</v>
       </c>
       <c r="D238" t="n">
-        <v>13.5</v>
+        <v>15.2</v>
       </c>
       <c r="E238" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="F238" t="n">
-        <v>4150</v>
+        <v>6300</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -7306,20 +7318,20 @@
         </is>
       </c>
       <c r="C239" t="n">
-        <v>49.2</v>
+        <v>46.2</v>
       </c>
       <c r="D239" t="n">
-        <v>15.2</v>
+        <v>14.5</v>
       </c>
       <c r="E239" t="n">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="F239" t="n">
-        <v>6300</v>
+        <v>4800</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -7335,20 +7347,20 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>46.2</v>
+        <v>48.7</v>
       </c>
       <c r="D240" t="n">
-        <v>14.5</v>
+        <v>15.1</v>
       </c>
       <c r="E240" t="n">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="F240" t="n">
-        <v>4800</v>
+        <v>5350</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -7364,16 +7376,16 @@
         </is>
       </c>
       <c r="C241" t="n">
-        <v>48.7</v>
+        <v>50.2</v>
       </c>
       <c r="D241" t="n">
-        <v>15.1</v>
+        <v>14.3</v>
       </c>
       <c r="E241" t="n">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F241" t="n">
-        <v>5350</v>
+        <v>5700</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -7393,20 +7405,20 @@
         </is>
       </c>
       <c r="C242" t="n">
-        <v>50.2</v>
+        <v>45.1</v>
       </c>
       <c r="D242" t="n">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="E242" t="n">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F242" t="n">
-        <v>5700</v>
+        <v>5000</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -7422,16 +7434,16 @@
         </is>
       </c>
       <c r="C243" t="n">
-        <v>45.1</v>
+        <v>46.5</v>
       </c>
       <c r="D243" t="n">
         <v>14.5</v>
       </c>
       <c r="E243" t="n">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F243" t="n">
-        <v>5000</v>
+        <v>4400</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -7451,20 +7463,20 @@
         </is>
       </c>
       <c r="C244" t="n">
-        <v>46.5</v>
+        <v>46.3</v>
       </c>
       <c r="D244" t="n">
-        <v>14.5</v>
+        <v>15.8</v>
       </c>
       <c r="E244" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F244" t="n">
-        <v>4400</v>
+        <v>5050</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -7480,20 +7492,20 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>46.3</v>
+        <v>42.9</v>
       </c>
       <c r="D245" t="n">
-        <v>15.8</v>
+        <v>13.1</v>
       </c>
       <c r="E245" t="n">
         <v>215</v>
       </c>
       <c r="F245" t="n">
-        <v>5050</v>
+        <v>5000</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -7509,20 +7521,20 @@
         </is>
       </c>
       <c r="C246" t="n">
-        <v>42.9</v>
+        <v>46.1</v>
       </c>
       <c r="D246" t="n">
-        <v>13.1</v>
+        <v>15.1</v>
       </c>
       <c r="E246" t="n">
         <v>215</v>
       </c>
       <c r="F246" t="n">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -7538,22 +7550,18 @@
         </is>
       </c>
       <c r="C247" t="n">
-        <v>46.1</v>
+        <v>44.5</v>
       </c>
       <c r="D247" t="n">
-        <v>15.1</v>
+        <v>14.3</v>
       </c>
       <c r="E247" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F247" t="n">
-        <v>5100</v>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
+        <v>4100</v>
+      </c>
+      <c r="G247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -7567,18 +7575,22 @@
         </is>
       </c>
       <c r="C248" t="n">
-        <v>44.5</v>
+        <v>47.8</v>
       </c>
       <c r="D248" t="n">
-        <v>14.3</v>
+        <v>15</v>
       </c>
       <c r="E248" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F248" t="n">
-        <v>4100</v>
-      </c>
-      <c r="G248" t="inlineStr"/>
+        <v>5650</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -7592,20 +7604,20 @@
         </is>
       </c>
       <c r="C249" t="n">
-        <v>47.8</v>
+        <v>48.2</v>
       </c>
       <c r="D249" t="n">
-        <v>15</v>
+        <v>14.3</v>
       </c>
       <c r="E249" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F249" t="n">
-        <v>5650</v>
+        <v>4600</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -7621,20 +7633,20 @@
         </is>
       </c>
       <c r="C250" t="n">
-        <v>48.2</v>
+        <v>50</v>
       </c>
       <c r="D250" t="n">
-        <v>14.3</v>
+        <v>15.3</v>
       </c>
       <c r="E250" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="F250" t="n">
-        <v>4600</v>
+        <v>5550</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -7650,16 +7662,16 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>50</v>
+        <v>47.3</v>
       </c>
       <c r="D251" t="n">
         <v>15.3</v>
       </c>
       <c r="E251" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F251" t="n">
-        <v>5550</v>
+        <v>5250</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -7679,20 +7691,20 @@
         </is>
       </c>
       <c r="C252" t="n">
-        <v>47.3</v>
+        <v>42.8</v>
       </c>
       <c r="D252" t="n">
-        <v>15.3</v>
+        <v>14.2</v>
       </c>
       <c r="E252" t="n">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="F252" t="n">
-        <v>5250</v>
+        <v>4700</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -7708,16 +7720,16 @@
         </is>
       </c>
       <c r="C253" t="n">
-        <v>42.8</v>
+        <v>45.1</v>
       </c>
       <c r="D253" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="E253" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F253" t="n">
-        <v>4700</v>
+        <v>5050</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
@@ -7737,20 +7749,20 @@
         </is>
       </c>
       <c r="C254" t="n">
-        <v>45.1</v>
+        <v>59.6</v>
       </c>
       <c r="D254" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="E254" t="n">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="F254" t="n">
-        <v>5050</v>
+        <v>6050</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -7766,20 +7778,20 @@
         </is>
       </c>
       <c r="C255" t="n">
-        <v>59.6</v>
+        <v>49.1</v>
       </c>
       <c r="D255" t="n">
-        <v>17</v>
+        <v>14.8</v>
       </c>
       <c r="E255" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="F255" t="n">
-        <v>6050</v>
+        <v>5150</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -7795,20 +7807,20 @@
         </is>
       </c>
       <c r="C256" t="n">
-        <v>49.1</v>
+        <v>48.4</v>
       </c>
       <c r="D256" t="n">
-        <v>14.8</v>
+        <v>16.3</v>
       </c>
       <c r="E256" t="n">
         <v>220</v>
       </c>
       <c r="F256" t="n">
-        <v>5150</v>
+        <v>5400</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -7824,20 +7836,20 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>48.4</v>
+        <v>42.6</v>
       </c>
       <c r="D257" t="n">
-        <v>16.3</v>
+        <v>13.7</v>
       </c>
       <c r="E257" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="F257" t="n">
-        <v>5400</v>
+        <v>4950</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -7853,20 +7865,20 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>42.6</v>
+        <v>44.4</v>
       </c>
       <c r="D258" t="n">
-        <v>13.7</v>
+        <v>17.3</v>
       </c>
       <c r="E258" t="n">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F258" t="n">
-        <v>4950</v>
+        <v>5250</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -7882,20 +7894,20 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>44.4</v>
+        <v>44</v>
       </c>
       <c r="D259" t="n">
-        <v>17.3</v>
+        <v>13.6</v>
       </c>
       <c r="E259" t="n">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="F259" t="n">
-        <v>5250</v>
+        <v>4350</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -7911,20 +7923,20 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>44</v>
+        <v>48.7</v>
       </c>
       <c r="D260" t="n">
-        <v>13.6</v>
+        <v>15.7</v>
       </c>
       <c r="E260" t="n">
         <v>208</v>
       </c>
       <c r="F260" t="n">
-        <v>4350</v>
+        <v>5350</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -7940,20 +7952,20 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>48.7</v>
+        <v>42.7</v>
       </c>
       <c r="D261" t="n">
-        <v>15.7</v>
+        <v>13.7</v>
       </c>
       <c r="E261" t="n">
         <v>208</v>
       </c>
       <c r="F261" t="n">
-        <v>5350</v>
+        <v>3950</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -7969,20 +7981,20 @@
         </is>
       </c>
       <c r="C262" t="n">
-        <v>42.7</v>
+        <v>49.6</v>
       </c>
       <c r="D262" t="n">
-        <v>13.7</v>
+        <v>16</v>
       </c>
       <c r="E262" t="n">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="F262" t="n">
-        <v>3950</v>
+        <v>5700</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -7998,20 +8010,20 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>49.6</v>
+        <v>45.3</v>
       </c>
       <c r="D263" t="n">
-        <v>16</v>
+        <v>13.7</v>
       </c>
       <c r="E263" t="n">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="F263" t="n">
-        <v>5700</v>
+        <v>4300</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -8027,20 +8039,20 @@
         </is>
       </c>
       <c r="C264" t="n">
-        <v>45.3</v>
+        <v>49.6</v>
       </c>
       <c r="D264" t="n">
-        <v>13.7</v>
+        <v>15</v>
       </c>
       <c r="E264" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F264" t="n">
-        <v>4300</v>
+        <v>4750</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -8056,16 +8068,16 @@
         </is>
       </c>
       <c r="C265" t="n">
-        <v>49.6</v>
+        <v>50.5</v>
       </c>
       <c r="D265" t="n">
-        <v>15</v>
+        <v>15.9</v>
       </c>
       <c r="E265" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F265" t="n">
-        <v>4750</v>
+        <v>5550</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
@@ -8085,20 +8097,20 @@
         </is>
       </c>
       <c r="C266" t="n">
-        <v>50.5</v>
+        <v>43.6</v>
       </c>
       <c r="D266" t="n">
-        <v>15.9</v>
+        <v>13.9</v>
       </c>
       <c r="E266" t="n">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="F266" t="n">
-        <v>5550</v>
+        <v>4900</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -8114,16 +8126,16 @@
         </is>
       </c>
       <c r="C267" t="n">
-        <v>43.6</v>
+        <v>45.5</v>
       </c>
       <c r="D267" t="n">
         <v>13.9</v>
       </c>
       <c r="E267" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F267" t="n">
-        <v>4900</v>
+        <v>4200</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
@@ -8143,20 +8155,20 @@
         </is>
       </c>
       <c r="C268" t="n">
-        <v>45.5</v>
+        <v>50.5</v>
       </c>
       <c r="D268" t="n">
-        <v>13.9</v>
+        <v>15.9</v>
       </c>
       <c r="E268" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="F268" t="n">
-        <v>4200</v>
+        <v>5400</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -8172,20 +8184,20 @@
         </is>
       </c>
       <c r="C269" t="n">
-        <v>50.5</v>
+        <v>44.9</v>
       </c>
       <c r="D269" t="n">
-        <v>15.9</v>
+        <v>13.3</v>
       </c>
       <c r="E269" t="n">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F269" t="n">
-        <v>5400</v>
+        <v>5100</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -8201,20 +8213,20 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>44.9</v>
+        <v>45.2</v>
       </c>
       <c r="D270" t="n">
-        <v>13.3</v>
+        <v>15.8</v>
       </c>
       <c r="E270" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F270" t="n">
-        <v>5100</v>
+        <v>5300</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -8230,20 +8242,20 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>45.2</v>
+        <v>46.6</v>
       </c>
       <c r="D271" t="n">
-        <v>15.8</v>
+        <v>14.2</v>
       </c>
       <c r="E271" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F271" t="n">
-        <v>5300</v>
+        <v>4850</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -8259,20 +8271,20 @@
         </is>
       </c>
       <c r="C272" t="n">
-        <v>46.6</v>
+        <v>48.5</v>
       </c>
       <c r="D272" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="E272" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="F272" t="n">
-        <v>4850</v>
+        <v>5300</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -8288,20 +8300,20 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>48.5</v>
+        <v>45.1</v>
       </c>
       <c r="D273" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="E273" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="F273" t="n">
-        <v>5300</v>
+        <v>4400</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -8317,20 +8329,20 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>45.1</v>
+        <v>50.1</v>
       </c>
       <c r="D274" t="n">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="E274" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="F274" t="n">
-        <v>4400</v>
+        <v>5000</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -8346,20 +8358,20 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>50.1</v>
+        <v>46.5</v>
       </c>
       <c r="D275" t="n">
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="E275" t="n">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="F275" t="n">
-        <v>5000</v>
+        <v>4900</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -8375,20 +8387,20 @@
         </is>
       </c>
       <c r="C276" t="n">
-        <v>46.5</v>
+        <v>45</v>
       </c>
       <c r="D276" t="n">
-        <v>14.4</v>
+        <v>15.4</v>
       </c>
       <c r="E276" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="F276" t="n">
-        <v>4900</v>
+        <v>5050</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -8404,20 +8416,20 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>45</v>
+        <v>43.8</v>
       </c>
       <c r="D277" t="n">
-        <v>15.4</v>
+        <v>13.9</v>
       </c>
       <c r="E277" t="n">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="F277" t="n">
-        <v>5050</v>
+        <v>4300</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -8433,20 +8445,20 @@
         </is>
       </c>
       <c r="C278" t="n">
-        <v>43.8</v>
+        <v>45.5</v>
       </c>
       <c r="D278" t="n">
-        <v>13.9</v>
+        <v>15</v>
       </c>
       <c r="E278" t="n">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="F278" t="n">
-        <v>4300</v>
+        <v>5000</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -8462,20 +8474,20 @@
         </is>
       </c>
       <c r="C279" t="n">
-        <v>45.5</v>
+        <v>43.2</v>
       </c>
       <c r="D279" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="E279" t="n">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="F279" t="n">
-        <v>5000</v>
+        <v>4450</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -8491,20 +8503,20 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>43.2</v>
+        <v>50.4</v>
       </c>
       <c r="D280" t="n">
-        <v>14.5</v>
+        <v>15.3</v>
       </c>
       <c r="E280" t="n">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="F280" t="n">
-        <v>4450</v>
+        <v>5550</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -8520,20 +8532,20 @@
         </is>
       </c>
       <c r="C281" t="n">
-        <v>50.4</v>
+        <v>45.3</v>
       </c>
       <c r="D281" t="n">
-        <v>15.3</v>
+        <v>13.8</v>
       </c>
       <c r="E281" t="n">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="F281" t="n">
-        <v>5550</v>
+        <v>4200</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -8549,20 +8561,20 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>45.3</v>
+        <v>46.2</v>
       </c>
       <c r="D282" t="n">
-        <v>13.8</v>
+        <v>14.9</v>
       </c>
       <c r="E282" t="n">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="F282" t="n">
-        <v>4200</v>
+        <v>5300</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -8578,20 +8590,20 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>46.2</v>
+        <v>45.7</v>
       </c>
       <c r="D283" t="n">
-        <v>14.9</v>
+        <v>13.9</v>
       </c>
       <c r="E283" t="n">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="F283" t="n">
-        <v>5300</v>
+        <v>4400</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -8607,20 +8619,20 @@
         </is>
       </c>
       <c r="C284" t="n">
-        <v>45.7</v>
+        <v>54.3</v>
       </c>
       <c r="D284" t="n">
-        <v>13.9</v>
+        <v>15.7</v>
       </c>
       <c r="E284" t="n">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="F284" t="n">
-        <v>4400</v>
+        <v>5650</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -8636,20 +8648,20 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>54.3</v>
+        <v>45.8</v>
       </c>
       <c r="D285" t="n">
-        <v>15.7</v>
+        <v>14.2</v>
       </c>
       <c r="E285" t="n">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="F285" t="n">
-        <v>5650</v>
+        <v>4700</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -8665,20 +8677,20 @@
         </is>
       </c>
       <c r="C286" t="n">
-        <v>45.8</v>
+        <v>49.8</v>
       </c>
       <c r="D286" t="n">
-        <v>14.2</v>
+        <v>16.8</v>
       </c>
       <c r="E286" t="n">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="F286" t="n">
-        <v>4700</v>
+        <v>5700</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -8694,22 +8706,18 @@
         </is>
       </c>
       <c r="C287" t="n">
-        <v>49.8</v>
+        <v>46.2</v>
       </c>
       <c r="D287" t="n">
-        <v>16.8</v>
+        <v>14.4</v>
       </c>
       <c r="E287" t="n">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="F287" t="n">
-        <v>5700</v>
-      </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
+        <v>4650</v>
+      </c>
+      <c r="G287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -8723,18 +8731,22 @@
         </is>
       </c>
       <c r="C288" t="n">
-        <v>46.2</v>
+        <v>49.5</v>
       </c>
       <c r="D288" t="n">
-        <v>14.4</v>
+        <v>16.2</v>
       </c>
       <c r="E288" t="n">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="F288" t="n">
-        <v>4650</v>
-      </c>
-      <c r="G288" t="inlineStr"/>
+        <v>5800</v>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -8748,20 +8760,20 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>49.5</v>
+        <v>43.5</v>
       </c>
       <c r="D289" t="n">
-        <v>16.2</v>
+        <v>14.2</v>
       </c>
       <c r="E289" t="n">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="F289" t="n">
-        <v>5800</v>
+        <v>4700</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -8777,20 +8789,20 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>43.5</v>
+        <v>50.7</v>
       </c>
       <c r="D290" t="n">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="E290" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F290" t="n">
-        <v>4700</v>
+        <v>5550</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -8806,20 +8818,20 @@
         </is>
       </c>
       <c r="C291" t="n">
-        <v>50.7</v>
+        <v>47.7</v>
       </c>
       <c r="D291" t="n">
         <v>15</v>
       </c>
       <c r="E291" t="n">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="F291" t="n">
-        <v>5550</v>
+        <v>4750</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -8835,20 +8847,20 @@
         </is>
       </c>
       <c r="C292" t="n">
-        <v>47.7</v>
+        <v>46.4</v>
       </c>
       <c r="D292" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="E292" t="n">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F292" t="n">
-        <v>4750</v>
+        <v>5000</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8876,7 @@
         </is>
       </c>
       <c r="C293" t="n">
-        <v>46.4</v>
+        <v>48.2</v>
       </c>
       <c r="D293" t="n">
         <v>15.6</v>
@@ -8873,7 +8885,7 @@
         <v>221</v>
       </c>
       <c r="F293" t="n">
-        <v>5000</v>
+        <v>5100</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
@@ -8893,20 +8905,20 @@
         </is>
       </c>
       <c r="C294" t="n">
-        <v>48.2</v>
+        <v>46.5</v>
       </c>
       <c r="D294" t="n">
-        <v>15.6</v>
+        <v>14.8</v>
       </c>
       <c r="E294" t="n">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F294" t="n">
-        <v>5100</v>
+        <v>5200</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -8922,16 +8934,16 @@
         </is>
       </c>
       <c r="C295" t="n">
-        <v>46.5</v>
+        <v>46.4</v>
       </c>
       <c r="D295" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="E295" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F295" t="n">
-        <v>5200</v>
+        <v>4700</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
@@ -8951,20 +8963,20 @@
         </is>
       </c>
       <c r="C296" t="n">
-        <v>46.4</v>
+        <v>48.6</v>
       </c>
       <c r="D296" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E296" t="n">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="F296" t="n">
-        <v>4700</v>
+        <v>5800</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -8980,20 +8992,20 @@
         </is>
       </c>
       <c r="C297" t="n">
-        <v>48.6</v>
+        <v>47.5</v>
       </c>
       <c r="D297" t="n">
-        <v>16</v>
+        <v>14.2</v>
       </c>
       <c r="E297" t="n">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="F297" t="n">
-        <v>5800</v>
+        <v>4600</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -9009,20 +9021,20 @@
         </is>
       </c>
       <c r="C298" t="n">
-        <v>47.5</v>
+        <v>51.1</v>
       </c>
       <c r="D298" t="n">
-        <v>14.2</v>
+        <v>16.3</v>
       </c>
       <c r="E298" t="n">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="F298" t="n">
-        <v>4600</v>
+        <v>6000</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -9038,20 +9050,20 @@
         </is>
       </c>
       <c r="C299" t="n">
-        <v>51.1</v>
+        <v>45.2</v>
       </c>
       <c r="D299" t="n">
-        <v>16.3</v>
+        <v>13.8</v>
       </c>
       <c r="E299" t="n">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F299" t="n">
-        <v>6000</v>
+        <v>4750</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -9070,17 +9082,17 @@
         <v>45.2</v>
       </c>
       <c r="D300" t="n">
-        <v>13.8</v>
+        <v>16.4</v>
       </c>
       <c r="E300" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="F300" t="n">
-        <v>4750</v>
+        <v>5950</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -9096,20 +9108,20 @@
         </is>
       </c>
       <c r="C301" t="n">
-        <v>45.2</v>
+        <v>49.1</v>
       </c>
       <c r="D301" t="n">
-        <v>16.4</v>
+        <v>14.5</v>
       </c>
       <c r="E301" t="n">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="F301" t="n">
-        <v>5950</v>
+        <v>4625</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -9125,20 +9137,20 @@
         </is>
       </c>
       <c r="C302" t="n">
-        <v>49.1</v>
+        <v>52.5</v>
       </c>
       <c r="D302" t="n">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="E302" t="n">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="F302" t="n">
-        <v>4625</v>
+        <v>5450</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -9154,20 +9166,20 @@
         </is>
       </c>
       <c r="C303" t="n">
-        <v>52.5</v>
+        <v>47.4</v>
       </c>
       <c r="D303" t="n">
-        <v>15.6</v>
+        <v>14.6</v>
       </c>
       <c r="E303" t="n">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="F303" t="n">
-        <v>5450</v>
+        <v>4725</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -9183,20 +9195,20 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>47.4</v>
+        <v>50</v>
       </c>
       <c r="D304" t="n">
-        <v>14.6</v>
+        <v>15.9</v>
       </c>
       <c r="E304" t="n">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="F304" t="n">
-        <v>4725</v>
+        <v>5350</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -9212,20 +9224,20 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>50</v>
+        <v>44.9</v>
       </c>
       <c r="D305" t="n">
-        <v>15.9</v>
+        <v>13.8</v>
       </c>
       <c r="E305" t="n">
-        <v>224</v>
+        <v>212</v>
       </c>
       <c r="F305" t="n">
-        <v>5350</v>
+        <v>4750</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -9241,20 +9253,20 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>44.9</v>
+        <v>50.8</v>
       </c>
       <c r="D306" t="n">
-        <v>13.8</v>
+        <v>17.3</v>
       </c>
       <c r="E306" t="n">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="F306" t="n">
-        <v>4750</v>
+        <v>5600</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -9270,20 +9282,20 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>50.8</v>
+        <v>43.4</v>
       </c>
       <c r="D307" t="n">
-        <v>17.3</v>
+        <v>14.4</v>
       </c>
       <c r="E307" t="n">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="F307" t="n">
-        <v>5600</v>
+        <v>4600</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -9299,20 +9311,20 @@
         </is>
       </c>
       <c r="C308" t="n">
-        <v>43.4</v>
+        <v>51.3</v>
       </c>
       <c r="D308" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="E308" t="n">
         <v>218</v>
       </c>
       <c r="F308" t="n">
-        <v>4600</v>
+        <v>5300</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -9328,20 +9340,20 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>51.3</v>
+        <v>47.5</v>
       </c>
       <c r="D309" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="E309" t="n">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="F309" t="n">
-        <v>5300</v>
+        <v>4875</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -9357,20 +9369,20 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>47.5</v>
+        <v>52.1</v>
       </c>
       <c r="D310" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E310" t="n">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="F310" t="n">
-        <v>4875</v>
+        <v>5550</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -9386,20 +9398,20 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>52.1</v>
+        <v>47.5</v>
       </c>
       <c r="D311" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E311" t="n">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="F311" t="n">
-        <v>5550</v>
+        <v>4950</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -9415,20 +9427,20 @@
         </is>
       </c>
       <c r="C312" t="n">
-        <v>47.5</v>
+        <v>52.2</v>
       </c>
       <c r="D312" t="n">
-        <v>15</v>
+        <v>17.1</v>
       </c>
       <c r="E312" t="n">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="F312" t="n">
-        <v>4950</v>
+        <v>5400</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -9444,20 +9456,20 @@
         </is>
       </c>
       <c r="C313" t="n">
-        <v>52.2</v>
+        <v>45.5</v>
       </c>
       <c r="D313" t="n">
-        <v>17.1</v>
+        <v>14.5</v>
       </c>
       <c r="E313" t="n">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="F313" t="n">
-        <v>5400</v>
+        <v>4750</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -9473,20 +9485,20 @@
         </is>
       </c>
       <c r="C314" t="n">
-        <v>45.5</v>
+        <v>49.5</v>
       </c>
       <c r="D314" t="n">
-        <v>14.5</v>
+        <v>16.1</v>
       </c>
       <c r="E314" t="n">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="F314" t="n">
-        <v>4750</v>
+        <v>5650</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -9502,20 +9514,20 @@
         </is>
       </c>
       <c r="C315" t="n">
-        <v>49.5</v>
+        <v>44.5</v>
       </c>
       <c r="D315" t="n">
-        <v>16.1</v>
+        <v>14.7</v>
       </c>
       <c r="E315" t="n">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="F315" t="n">
-        <v>5650</v>
+        <v>4850</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -9531,20 +9543,20 @@
         </is>
       </c>
       <c r="C316" t="n">
-        <v>44.5</v>
+        <v>50.8</v>
       </c>
       <c r="D316" t="n">
-        <v>14.7</v>
+        <v>15.7</v>
       </c>
       <c r="E316" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="F316" t="n">
-        <v>4850</v>
+        <v>5200</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -9560,16 +9572,16 @@
         </is>
       </c>
       <c r="C317" t="n">
-        <v>50.8</v>
+        <v>49.4</v>
       </c>
       <c r="D317" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="E317" t="n">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="F317" t="n">
-        <v>5200</v>
+        <v>4925</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
@@ -9589,20 +9601,20 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>49.4</v>
+        <v>46.9</v>
       </c>
       <c r="D318" t="n">
-        <v>15.8</v>
+        <v>14.6</v>
       </c>
       <c r="E318" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F318" t="n">
-        <v>4925</v>
+        <v>4875</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -9618,16 +9630,16 @@
         </is>
       </c>
       <c r="C319" t="n">
-        <v>46.9</v>
+        <v>48.4</v>
       </c>
       <c r="D319" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="E319" t="n">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="F319" t="n">
-        <v>4875</v>
+        <v>4625</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
@@ -9647,20 +9659,20 @@
         </is>
       </c>
       <c r="C320" t="n">
-        <v>48.4</v>
+        <v>51.1</v>
       </c>
       <c r="D320" t="n">
-        <v>14.4</v>
+        <v>16.5</v>
       </c>
       <c r="E320" t="n">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="F320" t="n">
-        <v>4625</v>
+        <v>5250</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -9676,20 +9688,20 @@
         </is>
       </c>
       <c r="C321" t="n">
-        <v>51.1</v>
+        <v>48.5</v>
       </c>
       <c r="D321" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="E321" t="n">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="F321" t="n">
-        <v>5250</v>
+        <v>4850</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -9705,20 +9717,20 @@
         </is>
       </c>
       <c r="C322" t="n">
-        <v>48.5</v>
+        <v>55.9</v>
       </c>
       <c r="D322" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E322" t="n">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="F322" t="n">
-        <v>4850</v>
+        <v>5600</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -9734,20 +9746,20 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>55.9</v>
+        <v>47.2</v>
       </c>
       <c r="D323" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="E323" t="n">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="F323" t="n">
-        <v>5600</v>
+        <v>4975</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -9763,20 +9775,20 @@
         </is>
       </c>
       <c r="C324" t="n">
-        <v>47.2</v>
+        <v>49.1</v>
       </c>
       <c r="D324" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="E324" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="F324" t="n">
-        <v>4975</v>
+        <v>5500</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -9792,22 +9804,18 @@
         </is>
       </c>
       <c r="C325" t="n">
-        <v>49.1</v>
+        <v>47.3</v>
       </c>
       <c r="D325" t="n">
-        <v>15</v>
+        <v>13.8</v>
       </c>
       <c r="E325" t="n">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F325" t="n">
-        <v>5500</v>
-      </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
+        <v>4725</v>
+      </c>
+      <c r="G325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -9821,18 +9829,22 @@
         </is>
       </c>
       <c r="C326" t="n">
-        <v>47.3</v>
+        <v>46.8</v>
       </c>
       <c r="D326" t="n">
-        <v>13.8</v>
+        <v>16.1</v>
       </c>
       <c r="E326" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F326" t="n">
-        <v>4725</v>
-      </c>
-      <c r="G326" t="inlineStr"/>
+        <v>5500</v>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -9846,20 +9858,20 @@
         </is>
       </c>
       <c r="C327" t="n">
-        <v>46.8</v>
+        <v>41.7</v>
       </c>
       <c r="D327" t="n">
-        <v>16.1</v>
+        <v>14.7</v>
       </c>
       <c r="E327" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F327" t="n">
-        <v>5500</v>
+        <v>4700</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -9875,20 +9887,20 @@
         </is>
       </c>
       <c r="C328" t="n">
-        <v>41.7</v>
+        <v>53.4</v>
       </c>
       <c r="D328" t="n">
-        <v>14.7</v>
+        <v>15.8</v>
       </c>
       <c r="E328" t="n">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="F328" t="n">
-        <v>4700</v>
+        <v>5500</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -9904,20 +9916,20 @@
         </is>
       </c>
       <c r="C329" t="n">
-        <v>53.4</v>
+        <v>43.3</v>
       </c>
       <c r="D329" t="n">
-        <v>15.8</v>
+        <v>14</v>
       </c>
       <c r="E329" t="n">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="F329" t="n">
-        <v>5500</v>
+        <v>4575</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -9933,20 +9945,20 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>43.3</v>
+        <v>48.1</v>
       </c>
       <c r="D330" t="n">
-        <v>14</v>
+        <v>15.1</v>
       </c>
       <c r="E330" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F330" t="n">
-        <v>4575</v>
+        <v>5500</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -9962,20 +9974,20 @@
         </is>
       </c>
       <c r="C331" t="n">
-        <v>48.1</v>
+        <v>50.5</v>
       </c>
       <c r="D331" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="E331" t="n">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="F331" t="n">
-        <v>5500</v>
+        <v>5000</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -9991,20 +10003,20 @@
         </is>
       </c>
       <c r="C332" t="n">
-        <v>50.5</v>
+        <v>49.8</v>
       </c>
       <c r="D332" t="n">
-        <v>15.2</v>
+        <v>15.9</v>
       </c>
       <c r="E332" t="n">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="F332" t="n">
-        <v>5000</v>
+        <v>5950</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -10020,20 +10032,20 @@
         </is>
       </c>
       <c r="C333" t="n">
-        <v>49.8</v>
+        <v>43.5</v>
       </c>
       <c r="D333" t="n">
-        <v>15.9</v>
+        <v>15.2</v>
       </c>
       <c r="E333" t="n">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="F333" t="n">
-        <v>5950</v>
+        <v>4650</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -10049,20 +10061,20 @@
         </is>
       </c>
       <c r="C334" t="n">
-        <v>43.5</v>
+        <v>51.5</v>
       </c>
       <c r="D334" t="n">
-        <v>15.2</v>
+        <v>16.3</v>
       </c>
       <c r="E334" t="n">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="F334" t="n">
-        <v>4650</v>
+        <v>5500</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -10078,20 +10090,20 @@
         </is>
       </c>
       <c r="C335" t="n">
-        <v>51.5</v>
+        <v>46.2</v>
       </c>
       <c r="D335" t="n">
-        <v>16.3</v>
+        <v>14.1</v>
       </c>
       <c r="E335" t="n">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="F335" t="n">
-        <v>5500</v>
+        <v>4375</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -10107,20 +10119,20 @@
         </is>
       </c>
       <c r="C336" t="n">
-        <v>46.2</v>
+        <v>55.1</v>
       </c>
       <c r="D336" t="n">
-        <v>14.1</v>
+        <v>16</v>
       </c>
       <c r="E336" t="n">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="F336" t="n">
-        <v>4375</v>
+        <v>5850</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -10136,22 +10148,18 @@
         </is>
       </c>
       <c r="C337" t="n">
-        <v>55.1</v>
+        <v>44.5</v>
       </c>
       <c r="D337" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="E337" t="n">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="F337" t="n">
-        <v>5850</v>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
+        <v>4875</v>
+      </c>
+      <c r="G337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -10165,18 +10173,22 @@
         </is>
       </c>
       <c r="C338" t="n">
-        <v>44.5</v>
+        <v>48.8</v>
       </c>
       <c r="D338" t="n">
-        <v>15.7</v>
+        <v>16.2</v>
       </c>
       <c r="E338" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F338" t="n">
-        <v>4875</v>
-      </c>
-      <c r="G338" t="inlineStr"/>
+        <v>6000</v>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -10190,20 +10202,20 @@
         </is>
       </c>
       <c r="C339" t="n">
-        <v>48.8</v>
+        <v>47.2</v>
       </c>
       <c r="D339" t="n">
-        <v>16.2</v>
+        <v>13.7</v>
       </c>
       <c r="E339" t="n">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="F339" t="n">
-        <v>6000</v>
+        <v>4925</v>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -10219,16 +10231,16 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>47.2</v>
+        <v>46.8</v>
       </c>
       <c r="D340" t="n">
-        <v>13.7</v>
+        <v>14.3</v>
       </c>
       <c r="E340" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F340" t="n">
-        <v>4925</v>
+        <v>4850</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
@@ -10247,11 +10259,23 @@
           <t>Biscoe</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr"/>
-      <c r="D341" t="inlineStr"/>
-      <c r="E341" t="inlineStr"/>
-      <c r="F341" t="inlineStr"/>
-      <c r="G341" t="inlineStr"/>
+      <c r="C341" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="D341" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="E341" t="n">
+        <v>222</v>
+      </c>
+      <c r="F341" t="n">
+        <v>5750</v>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -10265,16 +10289,16 @@
         </is>
       </c>
       <c r="C342" t="n">
-        <v>46.8</v>
+        <v>45.2</v>
       </c>
       <c r="D342" t="n">
-        <v>14.3</v>
+        <v>14.8</v>
       </c>
       <c r="E342" t="n">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F342" t="n">
-        <v>4850</v>
+        <v>5200</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
@@ -10294,76 +10318,18 @@
         </is>
       </c>
       <c r="C343" t="n">
-        <v>50.4</v>
+        <v>49.9</v>
       </c>
       <c r="D343" t="n">
-        <v>15.7</v>
+        <v>16.1</v>
       </c>
       <c r="E343" t="n">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="F343" t="n">
-        <v>5750</v>
+        <v>5400</v>
       </c>
       <c r="G343" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>Gentoo</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Biscoe</t>
-        </is>
-      </c>
-      <c r="C344" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="D344" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="E344" t="n">
-        <v>212</v>
-      </c>
-      <c r="F344" t="n">
-        <v>5200</v>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>Gentoo</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Biscoe</t>
-        </is>
-      </c>
-      <c r="C345" t="n">
-        <v>49.9</v>
-      </c>
-      <c r="D345" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="E345" t="n">
-        <v>213</v>
-      </c>
-      <c r="F345" t="n">
-        <v>5400</v>
-      </c>
-      <c r="G345" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
